--- a/artfynd/A 27234-2026 artfynd.xlsx
+++ b/artfynd/A 27234-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261645</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261640</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,6 +1028,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261638</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1132,6 +1152,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261639</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1251,6 +1276,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261641</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1370,6 +1400,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261642</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1489,6 +1524,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261643</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1608,8 +1648,23 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261644</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 27234-2026 artfynd.xlsx
+++ b/artfynd/A 27234-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135261645</v>
       </c>
       <c r="B2" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135261640</v>
       </c>
       <c r="B3" t="n">
-        <v>79397</v>
+        <v>79435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135261638</v>
       </c>
       <c r="B4" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>135261639</v>
       </c>
       <c r="B5" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>135261641</v>
       </c>
       <c r="B6" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>135261642</v>
       </c>
       <c r="B7" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>135261643</v>
       </c>
       <c r="B8" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>135261644</v>
       </c>
       <c r="B9" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 27234-2026 artfynd.xlsx
+++ b/artfynd/A 27234-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135261645</v>
       </c>
       <c r="B2" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135261640</v>
       </c>
       <c r="B3" t="n">
-        <v>79435</v>
+        <v>79462</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27234-2026 artfynd.xlsx
+++ b/artfynd/A 27234-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135261645</v>
       </c>
       <c r="B2" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
